--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4852,6 +4852,226 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120315888</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>599394</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6820649</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120315881</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91861</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>599420</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6820647</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4637,10 +4637,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119840701</v>
+        <v>119840695</v>
       </c>
       <c r="B34" t="n">
-        <v>90106</v>
+        <v>91879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4649,25 +4649,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5754</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4728,11 +4728,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4748,10 +4743,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840695</v>
+        <v>119840701</v>
       </c>
       <c r="B35" t="n">
-        <v>91861</v>
+        <v>90123</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4760,25 +4755,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4839,6 +4834,11 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120315888</v>
+        <v>120315881</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91879</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4866,44 +4866,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R36" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4960,10 +4968,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120315881</v>
+        <v>120315888</v>
       </c>
       <c r="B37" t="n">
-        <v>91861</v>
+        <v>91876</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4972,52 +4980,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599420</v>
+        <v>599394</v>
       </c>
       <c r="R37" t="n">
-        <v>6820647</v>
+        <v>6820649</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4637,10 +4637,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119840695</v>
+        <v>119840701</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>90123</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4649,25 +4649,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4728,6 +4728,11 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4743,10 +4748,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840701</v>
+        <v>119840695</v>
       </c>
       <c r="B35" t="n">
-        <v>90123</v>
+        <v>91879</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4755,25 +4760,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5754</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4833,11 +4838,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4637,10 +4637,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119840701</v>
+        <v>119840695</v>
       </c>
       <c r="B34" t="n">
-        <v>90123</v>
+        <v>91879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4649,25 +4649,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5754</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4728,11 +4728,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4748,10 +4743,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840695</v>
+        <v>119840701</v>
       </c>
       <c r="B35" t="n">
-        <v>91879</v>
+        <v>90123</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4760,25 +4755,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4838,6 +4833,11 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4854,10 +4854,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120315881</v>
+        <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>91879</v>
+        <v>91876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4866,52 +4866,44 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599420</v>
+        <v>599394</v>
       </c>
       <c r="R36" t="n">
-        <v>6820647</v>
+        <v>6820649</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4968,10 +4960,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120315888</v>
+        <v>120315881</v>
       </c>
       <c r="B37" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4980,44 +4972,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R37" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4854,10 +4854,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120315888</v>
+        <v>120315881</v>
       </c>
       <c r="B36" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4866,44 +4866,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R36" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4960,10 +4968,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120315881</v>
+        <v>120315888</v>
       </c>
       <c r="B37" t="n">
-        <v>91879</v>
+        <v>91876</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4972,52 +4980,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599420</v>
+        <v>599394</v>
       </c>
       <c r="R37" t="n">
-        <v>6820647</v>
+        <v>6820649</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4746,7 +4746,7 @@
         <v>119840701</v>
       </c>
       <c r="B35" t="n">
-        <v>90232</v>
+        <v>90242</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4746,7 +4746,7 @@
         <v>119840701</v>
       </c>
       <c r="B35" t="n">
-        <v>90242</v>
+        <v>90254</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,11 +4857,11 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>91929</v>
+        <v>92251</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,7 +4857,7 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,7 +4857,7 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,7 +4857,7 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,7 +4857,7 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4857,7 +4857,7 @@
         <v>120315888</v>
       </c>
       <c r="B36" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119358749</v>
+        <v>119358627</v>
       </c>
       <c r="B28" t="n">
-        <v>91859</v>
+        <v>90106</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3934,32 +3934,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1440</v>
+        <v>5754</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3969,17 +3965,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R28" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4013,7 +4009,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Återfynd på samma plats som när jag hittade den 2019 då var det två exemplar un återkom den mycket glädjande</t>
+          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4051,10 +4047,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119358627</v>
+        <v>119358686</v>
       </c>
       <c r="B29" t="n">
-        <v>90106</v>
+        <v>86333</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4063,28 +4059,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5754</v>
+        <v>1980</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -4094,17 +4094,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599420</v>
+        <v>599394</v>
       </c>
       <c r="R29" t="n">
-        <v>6820647</v>
+        <v>6820649</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4134,11 +4134,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4176,10 +4171,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119358686</v>
+        <v>119358573</v>
       </c>
       <c r="B30" t="n">
-        <v>86333</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4188,32 +4183,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1980</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -4223,17 +4214,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R30" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4263,6 +4254,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4300,7 +4296,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119358573</v>
+        <v>119415539</v>
       </c>
       <c r="B31" t="n">
         <v>91858</v>
@@ -4334,11 +4330,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -4347,13 +4339,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599420</v>
+        <v>599422</v>
       </c>
       <c r="R31" t="n">
-        <v>6820647</v>
+        <v>6820645</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4377,17 +4369,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4400,35 +4387,25 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119415539</v>
+        <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91859</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4437,25 +4414,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4368</v>
+        <v>1440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4468,10 +4445,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599422</v>
+        <v>599418</v>
       </c>
       <c r="R32" t="n">
-        <v>6820645</v>
+        <v>6820639</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4531,10 +4508,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119415871</v>
+        <v>119840695</v>
       </c>
       <c r="B33" t="n">
-        <v>91859</v>
+        <v>91879</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4543,25 +4520,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4570,17 +4547,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599418</v>
+        <v>599416</v>
       </c>
       <c r="R33" t="n">
-        <v>6820639</v>
+        <v>6820643</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4604,12 +4581,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4625,49 +4602,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119840695</v>
+        <v>119840701</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>90254</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4728,6 +4705,11 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4743,10 +4725,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840701</v>
+        <v>120315888</v>
       </c>
       <c r="B35" t="n">
-        <v>90254</v>
+        <v>92289</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4759,21 +4741,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4782,17 +4764,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599416</v>
+        <v>599394</v>
       </c>
       <c r="R35" t="n">
-        <v>6820643</v>
+        <v>6820649</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4816,12 +4798,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4833,11 +4815,6 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4854,56 +4831,64 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120315888</v>
+        <v>120315881</v>
       </c>
       <c r="B36" t="n">
-        <v>92287</v>
+        <v>91944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R36" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4957,120 +4942,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120315881</v>
-      </c>
-      <c r="B37" t="n">
-        <v>91944</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Bässe, Hls</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>599420</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6820647</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Enånger</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Alf Bjarne Roland Pallin</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Alf Bjarne Roland Pallin</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>92289</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4390,12 +4390,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>91859</v>
+        <v>92290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4493,15 +4493,20 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Bland gammal gran</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92520</v>
+        <v>92527</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92527</v>
+        <v>92536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92536</v>
+        <v>92540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92540</v>
+        <v>92542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Söder om Storåsen, Bässe, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92542</v>
+        <v>92544</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92544</v>
+        <v>92546</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4299,7 +4299,7 @@
         <v>119415539</v>
       </c>
       <c r="B31" t="n">
-        <v>92546</v>
+        <v>92550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4400,7 +4400,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>92554</v>
+        <v>92628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4400,7 +4400,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>92628</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4400,7 +4400,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4400,7 +4400,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>92635</v>
+        <v>92639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,6 +4938,112 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127756236</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>söder Storåsen, Bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>599441</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6820687</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Flera frk nere i sluttning ovanför spåret</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4974,7 +4974,7 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>söder Storåsen, Bässe, Hls</t>
+          <t>norr Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92646</v>
+        <v>92649</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92649</v>
+        <v>92657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>norr Bässeravinen, Hls</t>
+          <t>norr om spåret Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -5049,7 +5049,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92661</v>
+        <v>92669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91130</v>
+        <v>91133</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91130</v>
+        <v>91133</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5468,32 +5468,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>92667</v>
+        <v>92684</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5542,11 +5542,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5574,32 +5569,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B43" t="n">
-        <v>92682</v>
+        <v>92669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5612,10 +5607,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5648,6 +5643,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4943,7 +4943,7 @@
         <v>127756236</v>
       </c>
       <c r="B37" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92669</v>
+        <v>92761</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89410</v>
+        <v>89502</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91133</v>
+        <v>91225</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91133</v>
+        <v>91225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5468,32 +5468,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92684</v>
+        <v>92761</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5542,6 +5542,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5569,32 +5574,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92669</v>
+        <v>92776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5607,10 +5612,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R43" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5643,11 +5648,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,12 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>97655</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99941</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599466.3698077917</v>
+        <v>599466</v>
       </c>
       <c r="R15" t="n">
-        <v>6820715.348996798</v>
+        <v>6820715</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2410,19 +2405,9 @@
           <t>2008-04-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2008-04-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99941</v>
+        <v>99947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92761</v>
+        <v>92773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89502</v>
+        <v>89514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91225</v>
+        <v>91237</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91225</v>
+        <v>91237</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,11 +5527,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5559,32 +5554,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B43" t="n">
-        <v>92776</v>
+        <v>92773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5633,6 +5628,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99947</v>
+        <v>99950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92773</v>
+        <v>92775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89514</v>
+        <v>89516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92788</v>
+        <v>92775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,6 +5527,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,32 +5559,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92773</v>
+        <v>92790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R43" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5628,11 +5633,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99950</v>
+        <v>99955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>92775</v>
+        <v>92790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,11 +5527,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5559,32 +5554,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B43" t="n">
-        <v>92790</v>
+        <v>92775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5633,6 +5628,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99955</v>
+        <v>99956</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92790</v>
+        <v>92776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,6 +5527,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,32 +5559,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92775</v>
+        <v>92791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R43" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5628,11 +5633,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99956</v>
+        <v>99983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92776</v>
+        <v>92803</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89516</v>
+        <v>89543</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92776</v>
+        <v>92803</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99983</v>
+        <v>99989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99989</v>
+        <v>99996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>128316398</v>
       </c>
       <c r="B38" t="n">
-        <v>92803</v>
+        <v>92813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89543</v>
+        <v>89553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91267</v>
+        <v>91277</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91267</v>
+        <v>91277</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>92803</v>
+        <v>92830</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,11 +5527,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5559,32 +5554,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B43" t="n">
-        <v>92818</v>
+        <v>92813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5633,6 +5628,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92830</v>
+        <v>92813</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,6 +5527,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,32 +5559,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92813</v>
+        <v>92830</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R43" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5628,11 +5633,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>99996</v>
+        <v>100000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>92813</v>
+        <v>92830</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,11 +5527,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5559,32 +5554,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B43" t="n">
-        <v>92830</v>
+        <v>92813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5633,6 +5628,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89553</v>
+        <v>89557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92830</v>
+        <v>92817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599297</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820733</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5527,6 +5527,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5554,32 +5559,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377901</v>
+        <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92813</v>
+        <v>92834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599297</v>
+        <v>599342</v>
       </c>
       <c r="R43" t="n">
-        <v>6820733</v>
+        <v>6820709</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5628,11 +5633,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>100000</v>
+        <v>100007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>128378113</v>
       </c>
       <c r="B39" t="n">
-        <v>89557</v>
+        <v>89562</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>128377763</v>
       </c>
       <c r="B40" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>128377835</v>
       </c>
       <c r="B41" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>128377901</v>
       </c>
       <c r="B42" t="n">
-        <v>92817</v>
+        <v>92822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>100010</v>
+        <v>100015</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2335,7 +2335,7 @@
         <v>82507673</v>
       </c>
       <c r="B15" t="n">
-        <v>100015</v>
+        <v>100023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4385,7 +4385,7 @@
         <v>119415871</v>
       </c>
       <c r="B32" t="n">
-        <v>92639</v>
+        <v>92628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>92839</v>
+        <v>93216</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>6820709</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93234</v>
+        <v>93236</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93236</v>
+        <v>93237</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93237</v>
+        <v>93240</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93240</v>
+        <v>93241</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -5562,7 +5562,7 @@
         <v>128377662</v>
       </c>
       <c r="B43" t="n">
-        <v>93241</v>
+        <v>93242</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62134721</v>
+        <v>128378113</v>
       </c>
       <c r="B2" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599429.1886664587</v>
+        <v>599484</v>
       </c>
       <c r="R2" t="n">
-        <v>6820644.072503729</v>
+        <v>6820674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området. I år blir detta tredje platsen med kejsarskivling i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,60 +762,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62134720</v>
+        <v>95540464</v>
       </c>
       <c r="B3" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gulnande spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius rubicundulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Rea) A.Pearson</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,19 +816,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe sidsluttningen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599420.77681663</v>
+        <v>599340</v>
       </c>
       <c r="R3" t="n">
-        <v>6820637.144582171</v>
+        <v>6820724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,27 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>konfirmerad av Lennart Söderberg</t>
+          <t>Ett exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,38 +876,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>äldre kalkpåverkad lågörtsgranskog</t>
+          <t>Örtrik kalkgranskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62134723</v>
+        <v>82507673</v>
       </c>
       <c r="B4" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,46 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>643</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pollich) Holub</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Storåsen  nederst i sluttningen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599407.8178019228</v>
+        <v>599466</v>
       </c>
       <c r="R4" t="n">
-        <v>6820621.966651069</v>
+        <v>6820715</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,24 +968,19 @@
           <t>Enånger</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>DIN200804193002</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,80 +994,70 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+          <t>Fuktig örtrik granskog med hög bonitet</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Björn Wannberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anders Delin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62134727</v>
+        <v>68784058</v>
       </c>
       <c r="B5" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599405.9059272588</v>
+        <v>599592</v>
       </c>
       <c r="R5" t="n">
-        <v>6820621.911851429</v>
+        <v>6820787</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,22 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,7 +1100,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>stig i kalkpåverkad lågörtsgranskog</t>
+          <t>drygt 100-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2 substratenheter # förrötade granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,62 +1126,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62134718</v>
+        <v>79799546</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599395.9909395506</v>
+        <v>599394</v>
       </c>
       <c r="R6" t="n">
-        <v>6820634.046001132</v>
+        <v>6820649</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,22 +1202,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två gamla exemplar invid äldre grova granar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,82 +1225,76 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>mossvacka i äldre lågörtsgranskog</t>
+          <t>Rikare lågörtgranskog kalkpåverkad</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62134715</v>
+        <v>119415871</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>1440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599342.8936098409</v>
+        <v>599418</v>
       </c>
       <c r="R7" t="n">
-        <v>6820700.824602243</v>
+        <v>6820639</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,22 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,77 +1338,74 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+          <t>Bland gammal gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62134717</v>
+        <v>128316398</v>
       </c>
       <c r="B8" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>1440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599336.0103621794</v>
+        <v>599416</v>
       </c>
       <c r="R8" t="n">
-        <v>6820724.030607613</v>
+        <v>6820643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,22 +1432,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,82 +1451,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>frodig äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62134722</v>
+        <v>128377901</v>
       </c>
       <c r="B9" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>1440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599410.1255689109</v>
+        <v>599297</v>
       </c>
       <c r="R9" t="n">
-        <v>6820624.898570894</v>
+        <v>6820733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,22 +1538,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ny fyndplats i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,82 +1557,75 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62134716</v>
+        <v>97765512</v>
       </c>
       <c r="B10" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, stig mellan traktorväg och myr, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599336.7753736287</v>
+        <v>599425</v>
       </c>
       <c r="R10" t="n">
-        <v>6820714.022609246</v>
+        <v>6820644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1769,22 +1652,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inte hittats utanför ravinen tidigare</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,85 +1681,78 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>frodig äldre fuktig granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68784056</v>
+        <v>119358686</v>
       </c>
       <c r="B11" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>1980</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Porslinsblå spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cortinarius cumatilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599297.0355596516</v>
+        <v>599394</v>
       </c>
       <c r="R11" t="n">
-        <v>6820782.138077242</v>
+        <v>6820649</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1895,22 +1776,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1919,85 +1790,86 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68784055</v>
+        <v>62134721</v>
       </c>
       <c r="B12" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>1988</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599339.8066585899</v>
+        <v>599429</v>
       </c>
       <c r="R12" t="n">
-        <v>6820725.094576845</v>
+        <v>6820644</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,22 +1893,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,7 +1912,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
+          <t>äldre lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2068,15 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68784057</v>
+        <v>62134716</v>
       </c>
       <c r="B13" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,37 +1941,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599424.1820439729</v>
+        <v>599337</v>
       </c>
       <c r="R13" t="n">
-        <v>6820802.019555299</v>
+        <v>6820714</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2138,22 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,15 +2023,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>rel tät, högstammig granskog i sydlut</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>100 substratenheter # ca 120-åriga granar</t>
+          <t>frodig äldre fuktig granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2193,64 +2041,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79799546</v>
+        <v>62134722</v>
       </c>
       <c r="B14" t="n">
-        <v>90672</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1440</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599393.6414023958</v>
+        <v>599410</v>
       </c>
       <c r="R14" t="n">
-        <v>6820649.262694528</v>
+        <v>6820625</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2274,27 +2115,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två gamla exemplar invid äldre grova granar</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2303,77 +2129,74 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Rikare lågörtgranskog kalkpåverkad</t>
+          <t>äldre lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82507673</v>
+        <v>128377763</v>
       </c>
       <c r="B15" t="n">
-        <v>100023</v>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>643</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storåsen  nederst i sluttningen, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599466</v>
+        <v>599337</v>
       </c>
       <c r="R15" t="n">
-        <v>6820715</v>
+        <v>6820722</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2395,19 +2218,14 @@
           <t>Enånger</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>DIN200804193002</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2008-04-19</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2008-04-19</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2416,64 +2234,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Fuktig örtrik granskog med hög bonitet</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Wannberg</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Delin</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95488250</v>
+        <v>128377835</v>
       </c>
       <c r="B16" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2482,17 +2287,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bässeravinen, ovan myren, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599415.9851456159</v>
+        <v>599306</v>
       </c>
       <c r="R16" t="n">
-        <v>6820604.050820278</v>
+        <v>6820732</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2516,22 +2321,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2547,69 +2342,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Nilsson, Max Rosendahl</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95553012</v>
+        <v>128377846</v>
       </c>
       <c r="B17" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4368</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599416</v>
+        <v>599276</v>
       </c>
       <c r="R17" t="n">
-        <v>6820643</v>
+        <v>6820724</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2636,17 +2422,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt förekommer spridd över stora områden</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2659,40 +2440,25 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grannaturskog kalkpåverkad</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95540464</v>
+        <v>62134727</v>
       </c>
       <c r="B18" t="n">
-        <v>85275</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,21 +2466,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>464</v>
+        <v>4363</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnande spindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius rubicundulus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Rea) A.Pearson</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2724,21 +2490,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bässe sidsluttningen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599340.3256226286</v>
+        <v>599406</v>
       </c>
       <c r="R18" t="n">
-        <v>6820723.676600049</v>
+        <v>6820622</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2765,27 +2529,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett exemplar</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2794,93 +2543,74 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Örtrik kalkgranskog</t>
+          <t>stig i kalkpåverkad lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102521837</v>
+        <v>112306159</v>
       </c>
       <c r="B19" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599338.4088306368</v>
+        <v>599448</v>
       </c>
       <c r="R19" t="n">
-        <v>6820890.782655388</v>
+        <v>6820628</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2904,22 +2634,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Efter stigen i början nära vändplatsen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2928,33 +2653,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103359357</v>
+        <v>112306119</v>
       </c>
       <c r="B20" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2962,34 +2683,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599421.295826004</v>
+        <v>599416</v>
       </c>
       <c r="R20" t="n">
-        <v>6820635.726579958</v>
+        <v>6820643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3016,22 +2744,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3040,33 +2758,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103359356</v>
+        <v>62134723</v>
       </c>
       <c r="B21" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3074,34 +2788,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599421.295826004</v>
+        <v>599408</v>
       </c>
       <c r="R21" t="n">
-        <v>6820635.726579958</v>
+        <v>6820622</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3128,22 +2851,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,31 +2867,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103544149</v>
+        <v>95488250</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,45 +2899,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>Bässe norr om myren, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599447.3386667395</v>
+        <v>599416</v>
       </c>
       <c r="R22" t="n">
-        <v>6820628.35357967</v>
+        <v>6820604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3251,27 +2956,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Observatör Tomas Troschke</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3284,69 +2974,50 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>kalkpåverkad naturgranskog storåsens sydsluttning sydost om myren</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin, Tomas Troschke, Henrik Tykosson, Inga-Greta Andersson, Lena Westberg, Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97765512</v>
+        <v>95553012</v>
       </c>
       <c r="B23" t="n">
-        <v>83000</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1445</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3356,14 +3027,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bässe mellan stigen och myren, Lindefallet Enånger, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599425</v>
+        <v>599416</v>
       </c>
       <c r="R23" t="n">
-        <v>6820644</v>
+        <v>6820643</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3390,27 +3061,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Inte hittats utanför ravinen tidigare</t>
+          <t>Rikligt förekommer spridd över stora områden</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3423,30 +3084,35 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grannaturskog kalkpåverkad</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102521833</v>
+        <v>103359357</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3454,48 +3120,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599338.4088306368</v>
+        <v>599422</v>
       </c>
       <c r="R24" t="n">
-        <v>6820890.782655388</v>
+        <v>6820636</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3519,22 +3174,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3549,49 +3194,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112306119</v>
+        <v>119358573</v>
       </c>
       <c r="B25" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3604,14 +3244,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599416</v>
+        <v>599420</v>
       </c>
       <c r="R25" t="n">
-        <v>6820643</v>
+        <v>6820647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3638,12 +3278,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3655,6 +3300,16 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3671,15 +3326,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112306179</v>
+        <v>119415539</v>
       </c>
       <c r="B26" t="n">
-        <v>89155</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,44 +3337,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599447</v>
+        <v>599418</v>
       </c>
       <c r="R26" t="n">
-        <v>6820628</v>
+        <v>6820639</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3748,17 +3394,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Där stigen delar sig ned mot myren</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3771,62 +3412,47 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrblandskog kalkpåverkad.</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112306159</v>
+        <v>120315888</v>
       </c>
       <c r="B27" t="n">
-        <v>90851</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3835,17 +3461,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599447</v>
+        <v>599394</v>
       </c>
       <c r="R27" t="n">
-        <v>6820628</v>
+        <v>6820649</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3869,17 +3495,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Efter stigen i början nära vändplatsen</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3907,15 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119358627</v>
+        <v>127756236</v>
       </c>
       <c r="B28" t="n">
-        <v>90106</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,41 +3539,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>norr om spåret Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599420</v>
+        <v>599441</v>
       </c>
       <c r="R28" t="n">
-        <v>6820647</v>
+        <v>6820687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3984,17 +3596,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På samma plats som dofttaggsvampen</t>
+          <t>Flera frk nere i sluttning ovanför spåret</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,62 +3619,47 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119358686</v>
+        <v>62134717</v>
       </c>
       <c r="B29" t="n">
-        <v>86333</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1980</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Porslinsblå spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius cumatilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4072,24 +3669,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599394</v>
+        <v>599336</v>
       </c>
       <c r="R29" t="n">
-        <v>6820649</v>
+        <v>6820724</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4113,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4127,44 +3722,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>frodig äldre lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119358573</v>
+        <v>62134720</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,41 +3756,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599420</v>
+        <v>599421</v>
       </c>
       <c r="R30" t="n">
-        <v>6820647</v>
+        <v>6820637</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4233,17 +3819,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
+          <t>konfirmerad av Lennart Söderberg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4252,39 +3838,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>äldre kalkpåverkad lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119415539</v>
+        <v>103359356</v>
       </c>
       <c r="B31" t="n">
-        <v>92550</v>
+        <v>91443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4292,40 +3872,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söder om Storåsen, Bässe, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599418</v>
+        <v>599422</v>
       </c>
       <c r="R31" t="n">
-        <v>6820639</v>
+        <v>6820636</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4349,12 +3926,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4363,70 +3940,73 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119415871</v>
+        <v>112306179</v>
       </c>
       <c r="B32" t="n">
-        <v>92639</v>
+        <v>91443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1440</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söder Storåsen, Bässe, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599418</v>
+        <v>599448</v>
       </c>
       <c r="R32" t="n">
-        <v>6820639</v>
+        <v>6820628</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4450,12 +4030,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Där stigen delar sig ned mot myren</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,73 +4053,77 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Bland gammal gran</t>
+          <t>Barrblandskog kalkpåverkad.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119840695</v>
+        <v>119358627</v>
       </c>
       <c r="B33" t="n">
-        <v>91879</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599416</v>
+        <v>599420</v>
       </c>
       <c r="R33" t="n">
-        <v>6820643</v>
+        <v>6820647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4561,12 +4150,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4578,6 +4172,16 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4597,12 +4201,7 @@
         <v>119840701</v>
       </c>
       <c r="B34" t="n">
-        <v>90254</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,56 +4304,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120315888</v>
+        <v>119416410</v>
       </c>
       <c r="B35" t="n">
-        <v>92289</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4368</v>
+        <v>5836</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599394</v>
+        <v>599347</v>
       </c>
       <c r="R35" t="n">
-        <v>6820649</v>
+        <v>6820675</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4778,12 +4380,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4799,31 +4401,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120315881</v>
+        <v>62134715</v>
       </c>
       <c r="B36" t="n">
-        <v>91944</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4846,26 +4443,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599420</v>
+        <v>599343</v>
       </c>
       <c r="R36" t="n">
-        <v>6820647</v>
+        <v>6820701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4892,12 +4487,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4910,25 +4505,30 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127756236</v>
+        <v>62134718</v>
       </c>
       <c r="B37" t="n">
-        <v>92760</v>
+        <v>93233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4936,40 +4536,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>norr om spåret Bässeravinen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599441</v>
+        <v>599396</v>
       </c>
       <c r="R37" t="n">
-        <v>6820687</v>
+        <v>6820634</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4993,17 +4599,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Flera frk nere i sluttning ovanför spåret</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5016,59 +4617,56 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>mossvacka i äldre lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128316398</v>
+        <v>119840695</v>
       </c>
       <c r="B38" t="n">
-        <v>92813</v>
+        <v>93233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1440</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -5107,17 +4705,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5145,51 +4738,59 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128378113</v>
+        <v>120315881</v>
       </c>
       <c r="B39" t="n">
-        <v>89562</v>
+        <v>93233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>275</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599484</v>
+        <v>599420</v>
       </c>
       <c r="R39" t="n">
-        <v>6820674</v>
+        <v>6820647</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5213,17 +4814,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området. I år blir detta tredje platsen med kejsarskivling i området.</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5239,44 +4835,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128377763</v>
+        <v>128377662</v>
       </c>
       <c r="B40" t="n">
-        <v>91286</v>
+        <v>93307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5289,13 +4885,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599337</v>
+        <v>599342</v>
       </c>
       <c r="R40" t="n">
-        <v>6820722</v>
+        <v>6820709</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5352,48 +4948,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128377835</v>
+        <v>68784057</v>
       </c>
       <c r="B41" t="n">
-        <v>91286</v>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3215</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599306</v>
+        <v>599424</v>
       </c>
       <c r="R41" t="n">
-        <v>6820732</v>
+        <v>6820802</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5420,12 +5013,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5434,67 +5027,83 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>rel tät, högstammig granskog i sydlut</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>100 substratenheter # ca 120-åriga granar</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377901</v>
+        <v>82307781</v>
       </c>
       <c r="B42" t="n">
-        <v>92822</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1440</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässe myren norra kanten, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599297</v>
+        <v>599371</v>
       </c>
       <c r="R42" t="n">
-        <v>6820733</v>
+        <v>6820587</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5521,17 +5130,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ny fyndplats i området</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5544,66 +5148,89 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Blandmyr med barrträd</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Mindre myr med källdråg och tjärvedstubbar</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Tjärvedstubbe  av tall</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128377662</v>
+        <v>102521833</v>
       </c>
       <c r="B43" t="n">
-        <v>93242</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599342</v>
+        <v>599338</v>
       </c>
       <c r="R43" t="n">
-        <v>6820709</v>
+        <v>6820891</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5627,12 +5254,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5641,22 +5278,361 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>102521837</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 13021- 2022, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>599338</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6820891</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>68784055</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>599340</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6820725</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>68784056</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>599297</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6820782</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3451,10 +3451,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119415539</v>
+        <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93215</v>
+        <v>93363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>norr om myren Bässeravinen, Hls</t>
+          <t>norr om myren-söder om spåret, Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -3495,7 +3495,7 @@
         <v>6820639</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,7 +3551,7 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119415539</t>
+          <t>https://artportalen.se/Sighting/135793090</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93363</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>127756236</v>
       </c>
       <c r="B28" t="n">
-        <v>93215</v>
+        <v>93390</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>norr om spåret Bässeravinen, Hls</t>
+          <t>norr om spåret, Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera frk nere i sluttning ovanför spåret</t>
+          <t>Flera fruktkroppar i sluttning ovanför spåret</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3774,54 +3774,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>62134717</v>
+        <v>136261579</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>93390</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599336</v>
+        <v>599442</v>
       </c>
       <c r="R29" t="n">
-        <v>6820724</v>
+        <v>6820676</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3848,12 +3842,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,60 +3856,56 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>frodig äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134717</t>
+          <t>https://artportalen.se/Sighting/136261579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62134720</v>
+        <v>62134717</v>
       </c>
       <c r="B30" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599421</v>
+        <v>599336</v>
       </c>
       <c r="R30" t="n">
-        <v>6820637</v>
+        <v>6820724</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3972,11 +3962,6 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>konfirmerad av Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3988,7 +3973,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>äldre kalkpåverkad lågörtsgranskog</t>
+          <t>frodig äldre lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4005,13 +3990,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134720</t>
+          <t>https://artportalen.se/Sighting/62134717</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103359356</v>
+        <v>62134720</v>
       </c>
       <c r="B31" t="n">
         <v>91443</v>
@@ -4039,17 +4024,26 @@
           <t>(Bres.) Corner</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599422</v>
+        <v>599421</v>
       </c>
       <c r="R31" t="n">
-        <v>6820636</v>
+        <v>6820637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4076,12 +4070,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>konfirmerad av Lennart Söderberg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,28 +4091,33 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre kalkpåverkad lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103359356</t>
+          <t>https://artportalen.se/Sighting/62134720</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112306179</v>
+        <v>103359356</v>
       </c>
       <c r="B32" t="n">
         <v>91443</v>
@@ -4142,23 +4146,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599448</v>
+        <v>599422</v>
       </c>
       <c r="R32" t="n">
-        <v>6820628</v>
+        <v>6820636</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,17 +4182,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Där stigen delar sig ned mot myren</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,41 +4196,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Barrblandskog kalkpåverkad.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112306179</t>
+          <t>https://artportalen.se/Sighting/103359356</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119358627</v>
+        <v>112306179</v>
       </c>
       <c r="B33" t="n">
         <v>91443</v>
@@ -4276,14 +4257,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599420</v>
+        <v>599448</v>
       </c>
       <c r="R33" t="n">
-        <v>6820647</v>
+        <v>6820628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4310,17 +4291,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På samma plats som dofttaggsvampen</t>
+          <t>Där stigen delar sig ned mot myren</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,7 +4321,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>Barrblandskog kalkpåverkad.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4357,13 +4338,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119358627</t>
+          <t>https://artportalen.se/Sighting/112306179</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119840701</v>
+        <v>119358627</v>
       </c>
       <c r="B34" t="n">
         <v>91443</v>
@@ -4392,19 +4373,23 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599416</v>
+        <v>599420</v>
       </c>
       <c r="R34" t="n">
-        <v>6820643</v>
+        <v>6820647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4431,12 +4416,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4454,6 +4444,11 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4468,65 +4463,57 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840701</t>
+          <t>https://artportalen.se/Sighting/119358627</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119416410</v>
+        <v>119840701</v>
       </c>
       <c r="B35" t="n">
-        <v>92928</v>
+        <v>91443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5836</v>
+        <v>5754</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>norr om myren Bässeravinen, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599347</v>
+        <v>599416</v>
       </c>
       <c r="R35" t="n">
-        <v>6820675</v>
+        <v>6820643</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4550,12 +4537,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,30 +4555,35 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119416410</t>
+          <t>https://artportalen.se/Sighting/119840701</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>62134715</v>
+        <v>136261392</v>
       </c>
       <c r="B36" t="n">
-        <v>93233</v>
+        <v>91594</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,43 +4591,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599343</v>
+        <v>599408</v>
       </c>
       <c r="R36" t="n">
-        <v>6820701</v>
+        <v>6820625</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4662,12 +4648,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4680,82 +4666,79 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134715</t>
+          <t>https://artportalen.se/Sighting/136261392</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>62134718</v>
+        <v>119416410</v>
       </c>
       <c r="B37" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599396</v>
+        <v>599347</v>
       </c>
       <c r="R37" t="n">
-        <v>6820634</v>
+        <v>6820675</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4779,12 +4762,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4797,32 +4780,27 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>mossvacka i äldre lågörtsgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134718</t>
+          <t>https://artportalen.se/Sighting/119416410</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119840695</v>
+        <v>62134715</v>
       </c>
       <c r="B38" t="n">
         <v>93233</v>
@@ -4850,20 +4828,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599416</v>
+        <v>599343</v>
       </c>
       <c r="R38" t="n">
-        <v>6820643</v>
+        <v>6820701</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4890,12 +4874,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,27 +4892,32 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840695</t>
+          <t>https://artportalen.se/Sighting/62134715</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120315881</v>
+        <v>62134718</v>
       </c>
       <c r="B39" t="n">
         <v>93233</v>
@@ -4958,26 +4947,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599420</v>
+        <v>599396</v>
       </c>
       <c r="R39" t="n">
-        <v>6820647</v>
+        <v>6820634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5004,12 +4991,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,30 +5009,35 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>mossvacka i äldre lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120315881</t>
+          <t>https://artportalen.se/Sighting/62134718</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128377662</v>
+        <v>119840695</v>
       </c>
       <c r="B40" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5076,14 +5068,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599342</v>
+        <v>599416</v>
       </c>
       <c r="R40" t="n">
-        <v>6820709</v>
+        <v>6820643</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5110,12 +5102,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5131,27 +5123,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128377662</t>
+          <t>https://artportalen.se/Sighting/119840695</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>68784057</v>
+        <v>120315881</v>
       </c>
       <c r="B41" t="n">
-        <v>75428</v>
+        <v>93233</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5159,37 +5151,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599424</v>
+        <v>599420</v>
       </c>
       <c r="R41" t="n">
-        <v>6820802</v>
+        <v>6820647</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5213,12 +5216,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5227,46 +5230,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>rel tät, högstammig granskog i sydlut</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>100 substratenheter # ca 120-åriga granar</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784057</t>
+          <t>https://artportalen.se/Sighting/120315881</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>82307781</v>
+        <v>128377662</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>93307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5274,44 +5265,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bässe myren norra kanten, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599371</v>
+        <v>599342</v>
       </c>
       <c r="R42" t="n">
-        <v>6820587</v>
+        <v>6820709</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5335,12 +5322,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5353,45 +5340,30 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Blandmyr med barrträd</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Mindre myr med källdråg och tjärvedstubbar</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Tjärvedstubbe  av tall</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82307781</t>
+          <t>https://artportalen.se/Sighting/128377662</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>102521833</v>
+        <v>68784057</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5399,45 +5371,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599338</v>
+        <v>599424</v>
       </c>
       <c r="R43" t="n">
-        <v>6820891</v>
+        <v>6820802</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5464,22 +5425,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5490,31 +5441,44 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>rel tät, högstammig granskog i sydlut</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>100 substratenheter # ca 120-åriga granar</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521833</t>
+          <t>https://artportalen.se/Sighting/68784057</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102521837</v>
+        <v>82307781</v>
       </c>
       <c r="B44" t="n">
-        <v>58114</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5522,45 +5486,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässe myren norra kanten, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599338</v>
+        <v>599371</v>
       </c>
       <c r="R44" t="n">
-        <v>6820891</v>
+        <v>6820587</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5587,22 +5547,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5611,77 +5561,95 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Blandmyr med barrträd</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Mindre myr med källdråg och tjärvedstubbar</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Tjärvedstubbe  av tall</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521837</t>
+          <t>https://artportalen.se/Sighting/82307781</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>68784055</v>
+        <v>102521833</v>
       </c>
       <c r="B45" t="n">
-        <v>99142</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599340</v>
+        <v>599338</v>
       </c>
       <c r="R45" t="n">
-        <v>6820725</v>
+        <v>6820891</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5708,12 +5676,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,80 +5702,77 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784055</t>
+          <t>https://artportalen.se/Sighting/102521833</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68784056</v>
+        <v>102521837</v>
       </c>
       <c r="B46" t="n">
-        <v>99036</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>223591</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599297</v>
+        <v>599338</v>
       </c>
       <c r="R46" t="n">
-        <v>6820782</v>
+        <v>6820891</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5824,12 +5799,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5840,25 +5825,252 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>högstammig ca 110-årig granskog i sydsluttning</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102521837</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>68784055</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>599340</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6820725</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68784055</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>68784056</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>599297</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6820782</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68784056</t>
         </is>
@@ -5911,6 +6123,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>127756236</v>
       </c>
       <c r="B28" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>136261579</v>
       </c>
       <c r="B29" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>136261392</v>
       </c>
       <c r="B36" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>135793090</v>
       </c>
       <c r="B26" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>127756236</v>
       </c>
       <c r="B28" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>136261579</v>
       </c>
       <c r="B29" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>136261392</v>
       </c>
       <c r="B36" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,10 +2540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62134727</v>
+        <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>93193</v>
+        <v>91857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,43 +2551,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4363</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599406</v>
+        <v>599301</v>
       </c>
       <c r="R18" t="n">
-        <v>6820622</v>
+        <v>6820708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,12 +2608,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,38 +2622,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>stig i kalkpåverkad lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134727</t>
+          <t>https://artportalen.se/Sighting/136424364</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112306159</v>
+        <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>93193</v>
+        <v>91857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,21 +2657,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4363</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2690,14 +2680,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599448</v>
+        <v>599317</v>
       </c>
       <c r="R19" t="n">
-        <v>6820628</v>
+        <v>6820740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,17 +2714,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Efter stigen i början nära vändplatsen</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,69 +2735,71 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112306159</t>
+          <t>https://artportalen.se/Sighting/136424425</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112306119</v>
+        <v>62134727</v>
       </c>
       <c r="B20" t="n">
-        <v>93209</v>
+        <v>93193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599416</v>
+        <v>599406</v>
       </c>
       <c r="R20" t="n">
-        <v>6820643</v>
+        <v>6820622</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2839,12 +2826,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,78 +2840,76 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>stig i kalkpåverkad lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112306119</t>
+          <t>https://artportalen.se/Sighting/62134727</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>62134723</v>
+        <v>112306159</v>
       </c>
       <c r="B21" t="n">
-        <v>93215</v>
+        <v>93193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>4363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599408</v>
+        <v>599448</v>
       </c>
       <c r="R21" t="n">
-        <v>6820622</v>
+        <v>6820628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2951,12 +2936,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Efter stigen i början nära vändplatsen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,38 +2955,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134723</t>
+          <t>https://artportalen.se/Sighting/112306159</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95488250</v>
+        <v>112306119</v>
       </c>
       <c r="B22" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,37 +2990,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bässe norr om myren, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>599416</v>
       </c>
       <c r="R22" t="n">
-        <v>6820604</v>
+        <v>6820643</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,12 +3051,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,24 +3072,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95488250</t>
+          <t>https://artportalen.se/Sighting/112306119</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95553012</v>
+        <v>62134723</v>
       </c>
       <c r="B23" t="n">
         <v>93215</v>
@@ -3127,24 +3117,26 @@
           <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599416</v>
+        <v>599408</v>
       </c>
       <c r="R23" t="n">
-        <v>6820643</v>
+        <v>6820622</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,17 +3163,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt förekommer spridd över stora områden</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,41 +3177,35 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Grannaturskog kalkpåverkad</t>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95553012</t>
+          <t>https://artportalen.se/Sighting/62134723</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103359357</v>
+        <v>95488250</v>
       </c>
       <c r="B24" t="n">
         <v>93215</v>
@@ -3253,16 +3234,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>Bässe norr om myren, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599422</v>
+        <v>599416</v>
       </c>
       <c r="R24" t="n">
-        <v>6820636</v>
+        <v>6820604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3289,12 +3273,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,30 +3287,31 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103359357</t>
+          <t>https://artportalen.se/Sighting/95488250</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119358573</v>
+        <v>95553012</v>
       </c>
       <c r="B25" t="n">
         <v>93215</v>
@@ -3364,14 +3349,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599420</v>
+        <v>599416</v>
       </c>
       <c r="R25" t="n">
-        <v>6820647</v>
+        <v>6820643</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,17 +3383,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
+          <t>Rikligt förekommer spridd över stora områden</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,7 +3413,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>Grannaturskog kalkpåverkad</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3445,16 +3430,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119358573</t>
+          <t>https://artportalen.se/Sighting/95553012</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135793090</v>
+        <v>103359357</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,22 +3465,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>norr om myren-söder om spåret, Bässeravinen, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599418</v>
+        <v>599422</v>
       </c>
       <c r="R26" t="n">
-        <v>6820639</v>
+        <v>6820636</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,12 +3501,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,31 +3515,30 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135793090</t>
+          <t>https://artportalen.se/Sighting/103359357</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315888</v>
+        <v>119358573</v>
       </c>
       <c r="B27" t="n">
         <v>93215</v>
@@ -3586,22 +3567,26 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bässe mellan traktortvägen och myren, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599394</v>
+        <v>599420</v>
       </c>
       <c r="R27" t="n">
-        <v>6820649</v>
+        <v>6820647</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3625,12 +3610,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer i flera stora grupper mellan basvägen och stigen ned mot bäcken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,6 +3633,16 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3657,13 +3657,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120315888</t>
+          <t>https://artportalen.se/Sighting/119358573</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127756236</v>
+        <v>135793090</v>
       </c>
       <c r="B28" t="n">
         <v>93403</v>
@@ -3697,17 +3697,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>norr om spåret, Bässeravinen, Hls</t>
+          <t>norr om myren-söder om spåret, Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599441</v>
+        <v>599418</v>
       </c>
       <c r="R28" t="n">
-        <v>6820687</v>
+        <v>6820639</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3731,17 +3731,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i sluttning ovanför spåret</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,16 +3763,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127756236</t>
+          <t>https://artportalen.se/Sighting/135793090</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136261579</v>
+        <v>120315888</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,17 +3803,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe mellan traktortvägen och myren, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599442</v>
+        <v>599394</v>
       </c>
       <c r="R29" t="n">
-        <v>6820676</v>
+        <v>6820649</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3842,12 +3837,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3863,71 +3858,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136261579</t>
+          <t>https://artportalen.se/Sighting/120315888</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62134717</v>
+        <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>norr om spåret, Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599336</v>
+        <v>599441</v>
       </c>
       <c r="R30" t="n">
-        <v>6820724</v>
+        <v>6820687</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3954,12 +3943,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i sluttning ovanför spåret</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,38 +3962,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>frodig äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134717</t>
+          <t>https://artportalen.se/Sighting/127756236</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>62134720</v>
+        <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>91443</v>
+        <v>93403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4007,43 +3997,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599421</v>
+        <v>599442</v>
       </c>
       <c r="R31" t="n">
-        <v>6820637</v>
+        <v>6820676</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4070,17 +4054,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>konfirmerad av Lennart Söderberg</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,73 +4068,78 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>äldre kalkpåverkad lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134720</t>
+          <t>https://artportalen.se/Sighting/136261579</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103359356</v>
+        <v>62134717</v>
       </c>
       <c r="B32" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599422</v>
+        <v>599336</v>
       </c>
       <c r="R32" t="n">
-        <v>6820636</v>
+        <v>6820724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4182,12 +4166,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4198,28 +4182,33 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>frodig äldre lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103359356</t>
+          <t>https://artportalen.se/Sighting/62134717</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112306179</v>
+        <v>62134720</v>
       </c>
       <c r="B33" t="n">
         <v>91443</v>
@@ -4247,24 +4236,26 @@
           <t>(Bres.) Corner</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599448</v>
+        <v>599421</v>
       </c>
       <c r="R33" t="n">
-        <v>6820628</v>
+        <v>6820637</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4291,17 +4282,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Där stigen delar sig ned mot myren</t>
+          <t>konfirmerad av Lennart Söderberg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4310,41 +4301,35 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Barrblandskog kalkpåverkad.</t>
+          <t>äldre kalkpåverkad lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112306179</t>
+          <t>https://artportalen.se/Sighting/62134720</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119358627</v>
+        <v>103359356</v>
       </c>
       <c r="B34" t="n">
         <v>91443</v>
@@ -4373,23 +4358,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599420</v>
+        <v>599422</v>
       </c>
       <c r="R34" t="n">
-        <v>6820647</v>
+        <v>6820636</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4416,17 +4394,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På samma plats som dofttaggsvampen</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4435,41 +4408,30 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119358627</t>
+          <t>https://artportalen.se/Sighting/103359356</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119840701</v>
+        <v>112306179</v>
       </c>
       <c r="B35" t="n">
         <v>91443</v>
@@ -4498,19 +4460,23 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599416</v>
+        <v>599448</v>
       </c>
       <c r="R35" t="n">
-        <v>6820643</v>
+        <v>6820628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,12 +4503,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Där stigen delar sig ned mot myren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4560,6 +4531,11 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrblandskog kalkpåverkad.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4574,16 +4550,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840701</t>
+          <t>https://artportalen.se/Sighting/112306179</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136261392</v>
+        <v>119358627</v>
       </c>
       <c r="B36" t="n">
-        <v>91607</v>
+        <v>91443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4609,7 +4585,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4618,10 +4598,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599408</v>
+        <v>599420</v>
       </c>
       <c r="R36" t="n">
-        <v>6820625</v>
+        <v>6820647</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4648,12 +4628,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4666,79 +4651,81 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136261392</t>
+          <t>https://artportalen.se/Sighting/119358627</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119416410</v>
+        <v>119840701</v>
       </c>
       <c r="B37" t="n">
-        <v>92928</v>
+        <v>91443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5836</v>
+        <v>5754</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>norr om myren Bässeravinen, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599347</v>
+        <v>599416</v>
       </c>
       <c r="R37" t="n">
-        <v>6820675</v>
+        <v>6820643</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4762,12 +4749,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4780,30 +4767,35 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119416410</t>
+          <t>https://artportalen.se/Sighting/119840701</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>62134715</v>
+        <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>93233</v>
+        <v>91607</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,43 +4803,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599343</v>
+        <v>599408</v>
       </c>
       <c r="R38" t="n">
-        <v>6820701</v>
+        <v>6820625</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4874,12 +4860,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4892,82 +4878,79 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134715</t>
+          <t>https://artportalen.se/Sighting/136261392</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>62134718</v>
+        <v>119416410</v>
       </c>
       <c r="B39" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599396</v>
+        <v>599347</v>
       </c>
       <c r="R39" t="n">
-        <v>6820634</v>
+        <v>6820675</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4991,12 +4974,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,32 +4992,27 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>mossvacka i äldre lågörtsgranskog</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134718</t>
+          <t>https://artportalen.se/Sighting/119416410</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119840695</v>
+        <v>62134715</v>
       </c>
       <c r="B40" t="n">
         <v>93233</v>
@@ -5062,20 +5040,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599416</v>
+        <v>599343</v>
       </c>
       <c r="R40" t="n">
-        <v>6820643</v>
+        <v>6820701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5102,12 +5086,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5120,27 +5104,32 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840695</t>
+          <t>https://artportalen.se/Sighting/62134715</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120315881</v>
+        <v>62134718</v>
       </c>
       <c r="B41" t="n">
         <v>93233</v>
@@ -5170,26 +5159,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599420</v>
+        <v>599396</v>
       </c>
       <c r="R41" t="n">
-        <v>6820647</v>
+        <v>6820634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5216,12 +5203,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5234,30 +5221,35 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>mossvacka i äldre lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120315881</t>
+          <t>https://artportalen.se/Sighting/62134718</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128377662</v>
+        <v>119840695</v>
       </c>
       <c r="B42" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5288,14 +5280,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599342</v>
+        <v>599416</v>
       </c>
       <c r="R42" t="n">
-        <v>6820709</v>
+        <v>6820643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5322,12 +5314,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5343,27 +5335,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128377662</t>
+          <t>https://artportalen.se/Sighting/119840695</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>68784057</v>
+        <v>120315881</v>
       </c>
       <c r="B43" t="n">
-        <v>75428</v>
+        <v>93233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5371,37 +5363,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599424</v>
+        <v>599420</v>
       </c>
       <c r="R43" t="n">
-        <v>6820802</v>
+        <v>6820647</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5425,12 +5428,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5439,46 +5442,34 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>rel tät, högstammig granskog i sydlut</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>100 substratenheter # ca 120-åriga granar</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784057</t>
+          <t>https://artportalen.se/Sighting/120315881</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>82307781</v>
+        <v>128377662</v>
       </c>
       <c r="B44" t="n">
-        <v>79946</v>
+        <v>93307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5486,44 +5477,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bässe myren norra kanten, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599371</v>
+        <v>599342</v>
       </c>
       <c r="R44" t="n">
-        <v>6820587</v>
+        <v>6820709</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5547,12 +5534,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5565,45 +5552,30 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Blandmyr med barrträd</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Mindre myr med källdråg och tjärvedstubbar</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Tjärvedstubbe  av tall</t>
-        </is>
-      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82307781</t>
+          <t>https://artportalen.se/Sighting/128377662</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>102521833</v>
+        <v>68784057</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>75428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,45 +5583,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599338</v>
+        <v>599424</v>
       </c>
       <c r="R45" t="n">
-        <v>6820891</v>
+        <v>6820802</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5676,22 +5637,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5702,31 +5653,44 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>rel tät, högstammig granskog i sydlut</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>100 substratenheter # ca 120-åriga granar</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521833</t>
+          <t>https://artportalen.se/Sighting/68784057</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>102521837</v>
+        <v>82307781</v>
       </c>
       <c r="B46" t="n">
-        <v>58114</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,45 +5698,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässe myren norra kanten, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599338</v>
+        <v>599371</v>
       </c>
       <c r="R46" t="n">
-        <v>6820891</v>
+        <v>6820587</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5799,22 +5759,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5823,77 +5773,95 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Blandmyr med barrträd</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Mindre myr med källdråg och tjärvedstubbar</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Tjärvedstubbe  av tall</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521837</t>
+          <t>https://artportalen.se/Sighting/82307781</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>68784055</v>
+        <v>102521833</v>
       </c>
       <c r="B47" t="n">
-        <v>99142</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599340</v>
+        <v>599338</v>
       </c>
       <c r="R47" t="n">
-        <v>6820725</v>
+        <v>6820891</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5920,12 +5888,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5936,80 +5914,77 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784055</t>
+          <t>https://artportalen.se/Sighting/102521833</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>68784056</v>
+        <v>102521837</v>
       </c>
       <c r="B48" t="n">
-        <v>99036</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223591</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599297</v>
+        <v>599338</v>
       </c>
       <c r="R48" t="n">
-        <v>6820782</v>
+        <v>6820891</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6036,12 +6011,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6052,25 +6037,252 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>högstammig ca 110-årig granskog i sydsluttning</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102521837</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>68784055</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>599340</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6820725</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68784055</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>68784056</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>599297</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6820782</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68784056</t>
         </is>
@@ -6125,6 +6337,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91857</v>
+        <v>91858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91857</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>135793090</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>91871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
